--- a/Tabelas/criterios_por_regiao.xlsx
+++ b/Tabelas/criterios_por_regiao.xlsx
@@ -512,49 +512,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="C2" t="n">
-        <v>31.1</v>
+        <v>31.21</v>
       </c>
       <c r="D2" t="n">
-        <v>5.98</v>
+        <v>5.68</v>
       </c>
       <c r="E2" t="n">
-        <v>84.48</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>50.22</v>
+        <v>51.54</v>
       </c>
       <c r="G2" t="n">
-        <v>97.59</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>91.98</v>
+        <v>92.41</v>
       </c>
       <c r="I2" t="n">
-        <v>57.41</v>
+        <v>54.72</v>
       </c>
       <c r="J2" t="n">
-        <v>41.22</v>
+        <v>41.28</v>
       </c>
       <c r="K2" t="n">
-        <v>19.67</v>
+        <v>21.04</v>
       </c>
       <c r="L2" t="n">
-        <v>5.14</v>
+        <v>5.72</v>
       </c>
       <c r="M2" t="n">
-        <v>48.74</v>
+        <v>49.18</v>
       </c>
       <c r="N2" t="n">
-        <v>15.11</v>
+        <v>18.01</v>
       </c>
       <c r="O2" t="n">
-        <v>56.52</v>
+        <v>54.42</v>
       </c>
       <c r="P2" t="n">
-        <v>96.53</v>
+        <v>96.70999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -564,49 +564,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>35.31</v>
+        <v>35.72</v>
       </c>
       <c r="D3" t="n">
-        <v>6.35</v>
+        <v>5.68</v>
       </c>
       <c r="E3" t="n">
-        <v>83.3</v>
+        <v>85.09</v>
       </c>
       <c r="F3" t="n">
-        <v>58.17</v>
+        <v>60.62</v>
       </c>
       <c r="G3" t="n">
-        <v>95.34</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>88.97</v>
+        <v>90</v>
       </c>
       <c r="I3" t="n">
-        <v>52.73</v>
+        <v>47.87</v>
       </c>
       <c r="J3" t="n">
-        <v>45.16</v>
+        <v>46.42</v>
       </c>
       <c r="K3" t="n">
-        <v>18.9</v>
+        <v>22.58</v>
       </c>
       <c r="L3" t="n">
-        <v>6.3</v>
+        <v>7.58</v>
       </c>
       <c r="M3" t="n">
-        <v>57.09</v>
+        <v>57.4</v>
       </c>
       <c r="N3" t="n">
-        <v>13.51</v>
+        <v>18.51</v>
       </c>
       <c r="O3" t="n">
-        <v>56.52</v>
+        <v>53.26</v>
       </c>
       <c r="P3" t="n">
-        <v>96.90000000000001</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="4">
@@ -616,49 +616,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="C4" t="n">
-        <v>42.66</v>
+        <v>42.54</v>
       </c>
       <c r="D4" t="n">
-        <v>8.43</v>
+        <v>7.93</v>
       </c>
       <c r="E4" t="n">
-        <v>86.91</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>54.8</v>
+        <v>56.27</v>
       </c>
       <c r="G4" t="n">
-        <v>94.06999999999999</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>91.55</v>
+        <v>92.06</v>
       </c>
       <c r="I4" t="n">
-        <v>53.78</v>
+        <v>50.09</v>
       </c>
       <c r="J4" t="n">
-        <v>42.87</v>
+        <v>42.33</v>
       </c>
       <c r="K4" t="n">
-        <v>23.76</v>
+        <v>24.83</v>
       </c>
       <c r="L4" t="n">
-        <v>10.99</v>
+        <v>11.14</v>
       </c>
       <c r="M4" t="n">
-        <v>57.63</v>
+        <v>57.9</v>
       </c>
       <c r="N4" t="n">
-        <v>17.69</v>
+        <v>20.3</v>
       </c>
       <c r="O4" t="n">
-        <v>54.03</v>
+        <v>51.47</v>
       </c>
       <c r="P4" t="n">
-        <v>97.77</v>
+        <v>97.95</v>
       </c>
     </row>
     <row r="5">
@@ -668,49 +668,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="C5" t="n">
-        <v>41.14</v>
+        <v>41.19</v>
       </c>
       <c r="D5" t="n">
-        <v>4.84</v>
+        <v>4.65</v>
       </c>
       <c r="E5" t="n">
-        <v>80.2</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>46.85</v>
+        <v>48.06</v>
       </c>
       <c r="G5" t="n">
-        <v>97.37</v>
+        <v>96.8</v>
       </c>
       <c r="H5" t="n">
-        <v>86.37</v>
+        <v>86.84</v>
       </c>
       <c r="I5" t="n">
-        <v>59.42</v>
+        <v>57.29</v>
       </c>
       <c r="J5" t="n">
-        <v>35.59</v>
+        <v>35.37</v>
       </c>
       <c r="K5" t="n">
-        <v>14.09</v>
+        <v>14.86</v>
       </c>
       <c r="L5" t="n">
-        <v>5.1</v>
+        <v>5.19</v>
       </c>
       <c r="M5" t="n">
-        <v>54.86</v>
+        <v>54.93</v>
       </c>
       <c r="N5" t="n">
-        <v>10.74</v>
+        <v>12.18</v>
       </c>
       <c r="O5" t="n">
-        <v>59.39</v>
+        <v>58.18</v>
       </c>
       <c r="P5" t="n">
-        <v>97.34</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="6">
@@ -723,46 +723,46 @@
         <v>0.12</v>
       </c>
       <c r="C6" t="n">
-        <v>43.09</v>
+        <v>42.64</v>
       </c>
       <c r="D6" t="n">
-        <v>12.59</v>
+        <v>11.88</v>
       </c>
       <c r="E6" t="n">
-        <v>86.86</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>53.41</v>
+        <v>54.87</v>
       </c>
       <c r="G6" t="n">
-        <v>95.47</v>
+        <v>93.8</v>
       </c>
       <c r="H6" t="n">
-        <v>88.26000000000001</v>
+        <v>88.67</v>
       </c>
       <c r="I6" t="n">
-        <v>57.98</v>
+        <v>55.34</v>
       </c>
       <c r="J6" t="n">
-        <v>42.84</v>
+        <v>41.32</v>
       </c>
       <c r="K6" t="n">
-        <v>15.79</v>
+        <v>16.43</v>
       </c>
       <c r="L6" t="n">
-        <v>3.9</v>
+        <v>4.57</v>
       </c>
       <c r="M6" t="n">
-        <v>52.62</v>
+        <v>53.34</v>
       </c>
       <c r="N6" t="n">
-        <v>12.64</v>
+        <v>15.32</v>
       </c>
       <c r="O6" t="n">
-        <v>57.27</v>
+        <v>54.84</v>
       </c>
       <c r="P6" t="n">
-        <v>98.79000000000001</v>
+        <v>98.83</v>
       </c>
     </row>
   </sheetData>
